--- a/artfynd/A 13183-2023 artfynd.xlsx
+++ b/artfynd/A 13183-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13183-2023 artfynd.xlsx
+++ b/artfynd/A 13183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112159961</v>
+        <v>130910532</v>
       </c>
       <c r="B2" t="n">
-        <v>103818</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Intill Finnabäcken, Nrk</t>
+          <t>Getrikebergen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500898</v>
+        <v>501061</v>
       </c>
       <c r="R2" t="n">
-        <v>6544336</v>
+        <v>6544270</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,22 +763,233 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112159961</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Intill Finnabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>500897</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6544336</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Erik Elmqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Erik Elmqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112160138</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Intill Finnabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500838</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544247</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Elmqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Elmqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13183-2023 artfynd.xlsx
+++ b/artfynd/A 13183-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910532</t>
         </is>
       </c>
     </row>
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112159961</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112160138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>